--- a/patterns/results/exp2/cqrs-tradeoffs-results.xlsx
+++ b/patterns/results/exp2/cqrs-tradeoffs-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9602A73A-F29F-7E49-997C-F5141066BE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7885FF38-E786-C042-A321-C8110336D9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8120" yWindow="3280" windowWidth="28640" windowHeight="16660" activeTab="2" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
@@ -18,8 +18,11 @@
     <sheet name="CQRS-CLUSTERING" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_2bins_results_cqrs" localSheetId="0">'CQRS-2BINS'!$A$1:$G$11</definedName>
-    <definedName name="clustering_results_cqrs" localSheetId="2">'CQRS-CLUSTERING'!$A$1:$K$19</definedName>
+    <definedName name="_2bins_metrics_cqrs" localSheetId="0">'CQRS-2BINS'!$A$11:$L$13</definedName>
+    <definedName name="_2bins_results_cqrs" localSheetId="0">'CQRS-2BINS'!$A$1:$G$9</definedName>
+    <definedName name="clustering_metrics_cqrs" localSheetId="2">'CQRS-CLUSTERING'!$A$20:$L$22</definedName>
+    <definedName name="clustering_results_cqrs" localSheetId="2">'CQRS-CLUSTERING'!$A$1:$K$17</definedName>
+    <definedName name="pareto_metrics_cqrs" localSheetId="1">'CQRS-PARETO'!$A$19:$L$21</definedName>
     <definedName name="pareto_results_cqrs" localSheetId="1">'CQRS-PARETO'!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,9 +47,14 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{254E0448-0D43-3D4F-954F-3EE8FA634255}" name="2bins-results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/2bins-results-cqrs.csv" decimal="," thousands="." comma="1">
-      <textFields count="7">
+  <connection id="1" xr16:uid="{BB652ED5-8DD6-C245-89DA-20AAC9B9D3D8}" name="2bins-metrics-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/cqrs/2bins-metrics-cqrs.csv" thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
         <textField/>
         <textField/>
         <textField/>
@@ -57,13 +65,9 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{1D4249D2-07C3-1E42-9219-73BA8932CDDE}" name="clustering-results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/clustering-results-cqrs.csv" decimal="," thousands="." comma="1">
-      <textFields count="11">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
+  <connection id="2" xr16:uid="{254E0448-0D43-3D4F-954F-3EE8FA634255}" name="2bins-results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/cqrs/2bins-results-cqrs.csv" decimal="," thousands="." comma="1">
+      <textFields count="7">
         <textField/>
         <textField/>
         <textField/>
@@ -74,8 +78,61 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" xr16:uid="{B612A3CC-1156-204D-8CFF-7293AE05B82F}" name="pareto-results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/pareto-results-cqrs.csv" decimal="," thousands="." comma="1">
+  <connection id="3" xr16:uid="{871D9739-2719-6C48-AE6F-1323A9821C74}" name="clustering-metrics-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/cqrs/clustering-metrics-cqrs.csv" thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="4" xr16:uid="{1D4249D2-07C3-1E42-9219-73BA8932CDDE}" name="clustering-results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/cqrs/clustering-results-cqrs.csv" decimal="," thousands="." comma="1">
+      <textFields count="11">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="5" xr16:uid="{7C227686-85C1-CB4E-9526-E00DDD2C943A}" name="pareto-metrics-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/cqrs/pareto-metrics-cqrs.csv" thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="6" xr16:uid="{B612A3CC-1156-204D-8CFF-7293AE05B82F}" name="pareto-results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/cqrs/pareto-results-cqrs.csv" decimal="," thousands="." comma="1">
       <textFields count="7">
         <textField/>
         <textField/>
@@ -91,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="29">
   <si>
     <t>method</t>
   </si>
@@ -123,46 +180,61 @@
     <t>S-S</t>
   </si>
   <si>
-    <t>pareto-efficient-sub-optimal</t>
-  </si>
-  <si>
-    <t>pareto-efficient-pareto-efficient</t>
-  </si>
-  <si>
-    <t>sub-optimal-pareto-efficient</t>
-  </si>
-  <si>
-    <t>sub-optimal-sub-optimal</t>
-  </si>
-  <si>
-    <t>C1-C1</t>
-  </si>
-  <si>
-    <t>C1-C2</t>
-  </si>
-  <si>
-    <t>C2-C1</t>
-  </si>
-  <si>
-    <t>C2-C2</t>
-  </si>
-  <si>
     <t>hardware</t>
   </si>
   <si>
     <t>software</t>
   </si>
   <si>
-    <t>C3-C1</t>
+    <t>precision</t>
   </si>
   <si>
-    <t>C3-C2</t>
+    <t>recall</t>
   </si>
   <si>
-    <t>C4-C1</t>
+    <t>f1</t>
   </si>
   <si>
-    <t>C4-C2</t>
+    <t>lift</t>
+  </si>
+  <si>
+    <t>complexity</t>
+  </si>
+  <si>
+    <t>success_rate</t>
+  </si>
+  <si>
+    <t>precision_std</t>
+  </si>
+  <si>
+    <t>recall_std</t>
+  </si>
+  <si>
+    <t>f1_std</t>
+  </si>
+  <si>
+    <t>lift_std</t>
+  </si>
+  <si>
+    <t>complexity_std</t>
+  </si>
+  <si>
+    <t>M-L</t>
+  </si>
+  <si>
+    <t>M-S</t>
+  </si>
+  <si>
+    <t>X-S</t>
+  </si>
+  <si>
+    <t>X-X</t>
+  </si>
+  <si>
+    <t>XS-L</t>
+  </si>
+  <si>
+    <t>XS-XS</t>
   </si>
 </sst>
 </file>
@@ -221,13 +293,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="5"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -253,6 +318,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -260,12 +332,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -281,7 +347,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,7 +675,31 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -618,40 +714,20 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -663,19 +739,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -683,98 +759,124 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,16 +898,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>859691</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9768</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>535354</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>28330</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>291122</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -834,7 +936,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1250462" y="2667000"/>
+          <a:off x="1230922" y="3135922"/>
           <a:ext cx="7315200" cy="6388100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -851,23 +953,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>270933</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1126067</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>330199</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12D61C46-2669-8D42-3143-0ED0A9931BA2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47D4ACB5-1FB7-200E-FBA2-B7E0171CABD9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -889,7 +991,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1253067" y="4064000"/>
+          <a:off x="846666" y="4749800"/>
           <a:ext cx="7315200" cy="6388100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -907,22 +1009,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>205153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>27354</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>28331</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>37123</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>28330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4484DCDF-6E72-C846-8904-E4B1EB668368}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7104AC52-0576-07C5-898C-E1D5C82FA351}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -944,7 +1046,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1748692" y="4513385"/>
+          <a:off x="1778000" y="5539153"/>
           <a:ext cx="7315200" cy="6388100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -958,15 +1060,27 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2bins-results-cqrs" connectionId="1" xr16:uid="{02720742-AC99-204B-B1D1-E92ED6F6C4D8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2bins-metrics-cqrs" connectionId="1" xr16:uid="{D03ACEC5-CA05-A546-B8E9-7F623FC450D3}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="pareto-results-cqrs" connectionId="3" xr16:uid="{60DC4410-B58A-6741-B9BA-743D9B37B8EB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2bins-results-cqrs" connectionId="2" xr16:uid="{02720742-AC99-204B-B1D1-E92ED6F6C4D8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="clustering-results-cqrs" connectionId="2" xr16:uid="{29BD85F0-F3EA-D349-8E81-4792978CABCD}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="pareto-metrics-cqrs" connectionId="5" xr16:uid="{10F9BD07-5006-5A40-90DB-8078D1BE7A5E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="pareto-results-cqrs" connectionId="6" xr16:uid="{60DC4410-B58A-6741-B9BA-743D9B37B8EB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="clustering-metrics-cqrs" connectionId="3" xr16:uid="{38D23DB4-4370-0544-89D6-0B9ED70AE733}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="clustering-results-cqrs" connectionId="4" xr16:uid="{29BD85F0-F3EA-D349-8E81-4792978CABCD}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1289,16 +1403,17 @@
   <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" customWidth="1"/>
-    <col min="8" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
@@ -1342,16 +1457,16 @@
       <c r="S1" s="6"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="40"/>
+      <c r="B2" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="48"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="54">
+      <c r="F2" s="73">
         <v>0.87401574803149595</v>
       </c>
       <c r="G2" s="55">
@@ -1372,19 +1487,19 @@
       <c r="T2" s="8"/>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="44"/>
+      <c r="B3" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="52"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="22">
+      <c r="F3" s="53">
         <v>0</v>
       </c>
-      <c r="G3" s="56">
+      <c r="G3" s="69">
         <v>1</v>
       </c>
       <c r="H3" s="7"/>
@@ -1402,23 +1517,21 @@
       <c r="T3" s="8"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="B4" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="58">
+      <c r="F4" s="72">
         <v>1</v>
       </c>
-      <c r="G4" s="34">
-        <v>0</v>
-      </c>
+      <c r="G4" s="55"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -1434,21 +1547,21 @@
       <c r="T4" s="8"/>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="42" t="s">
+      <c r="B5" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="58" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="52">
+      <c r="F5" s="60">
         <v>0</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="66">
         <v>1</v>
       </c>
       <c r="H5" s="7"/>
@@ -1466,21 +1579,21 @@
       <c r="T5" s="8"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="B6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
-      <c r="F6" s="60">
+      <c r="F6" s="53">
         <v>0.79661016949152497</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="72">
         <v>0.20338983050847401</v>
       </c>
       <c r="H6" s="7"/>
@@ -1498,21 +1611,19 @@
       <c r="T6" s="8"/>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="43" t="s">
+      <c r="B7" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="37">
-        <v>0</v>
-      </c>
-      <c r="G7" s="59">
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="77">
         <v>1</v>
       </c>
       <c r="H7" s="7"/>
@@ -1530,22 +1641,20 @@
       <c r="T7" s="8"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="61">
-        <v>0.83333333333333304</v>
-      </c>
-      <c r="G8" s="62">
-        <v>0.16666666666666599</v>
+      <c r="B8" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="78"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="79">
+        <v>1</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1562,21 +1671,19 @@
       <c r="T8" s="8"/>
     </row>
     <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="52">
-        <v>0</v>
-      </c>
-      <c r="G9" s="63">
+      <c r="B9" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="80"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="74">
         <v>1</v>
       </c>
       <c r="H9" s="7"/>
@@ -1594,23 +1701,10 @@
       <c r="T9" s="8"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="22">
-        <v>0</v>
-      </c>
-      <c r="G10" s="58">
-        <v>1</v>
-      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
@@ -1625,29 +1719,41 @@
       <c r="S10" s="7"/>
       <c r="T10" s="8"/>
     </row>
-    <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="36" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="57"/>
+      <c r="B11" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="37">
-        <v>0</v>
-      </c>
-      <c r="G11" s="59">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="J11" s="82" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="82" t="s">
+        <v>22</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -1658,18 +1764,42 @@
       <c r="T11" s="8"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="A12" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="67">
+        <v>0.50164141414141405</v>
+      </c>
+      <c r="C12" s="67">
+        <v>0.35688101894998397</v>
+      </c>
+      <c r="D12" s="53">
+        <v>0.41645773063323599</v>
+      </c>
+      <c r="E12" s="67">
+        <v>1.64141414141416E-3</v>
+      </c>
+      <c r="F12" s="53">
+        <v>2</v>
+      </c>
+      <c r="G12" s="67">
+        <v>1</v>
+      </c>
+      <c r="H12" s="53">
+        <v>7.1085858585858502E-2</v>
+      </c>
+      <c r="I12" s="53">
+        <v>7.7601739670705105E-2</v>
+      </c>
+      <c r="J12" s="53">
+        <v>7.7659916425586603E-2</v>
+      </c>
+      <c r="K12" s="53">
+        <v>4.6796085858585804E-3</v>
+      </c>
+      <c r="L12" s="53">
+        <v>0</v>
+      </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -1680,18 +1810,42 @@
       <c r="T12" s="8"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="A13" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="67">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="67">
+        <v>4.4827586206896503E-2</v>
+      </c>
+      <c r="D13" s="53">
+        <v>8.2278481012658194E-2</v>
+      </c>
+      <c r="E13" s="67">
+        <v>0</v>
+      </c>
+      <c r="F13" s="53">
+        <v>1</v>
+      </c>
+      <c r="G13" s="67">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="53">
+        <v>4.4827586206896503E-2</v>
+      </c>
+      <c r="J13" s="53">
+        <v>8.2278481012658194E-2</v>
+      </c>
+      <c r="K13" s="53">
+        <v>0.43359375</v>
+      </c>
+      <c r="L13" s="53">
+        <v>0</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="12"/>
       <c r="O13" s="7"/>
@@ -1702,13 +1856,10 @@
       <c r="T13" s="8"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="22"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
@@ -1724,13 +1875,10 @@
       <c r="T14" s="8"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="22"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -1746,13 +1894,10 @@
       <c r="T15" s="8"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="22"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="20"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -1767,14 +1912,11 @@
       <c r="S16" s="11"/>
       <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
+    <row r="17" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="14"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1789,14 +1931,11 @@
       <c r="S17" s="7"/>
       <c r="T17" s="8"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="26"/>
+    <row r="18" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1811,14 +1950,11 @@
       <c r="S18" s="7"/>
       <c r="T18" s="8"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="25"/>
+    <row r="19" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -1833,7 +1969,7 @@
       <c r="S19" s="7"/>
       <c r="T19" s="8"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:20" x14ac:dyDescent="0.2">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -1852,7 +1988,7 @@
       <c r="S20" s="7"/>
       <c r="T20" s="8"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:20" x14ac:dyDescent="0.2">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1871,7 +2007,7 @@
       <c r="S21" s="7"/>
       <c r="T21" s="8"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:20" x14ac:dyDescent="0.2">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1890,7 +2026,7 @@
       <c r="S22" s="7"/>
       <c r="T22" s="8"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="4:20" x14ac:dyDescent="0.2">
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1909,11 +2045,11 @@
       <c r="S23" s="11"/>
       <c r="T23" s="8"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+    <row r="24" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D24" s="12"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
@@ -1928,11 +2064,11 @@
       <c r="S24" s="10"/>
       <c r="T24" s="8"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+    <row r="25" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D25" s="8"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
@@ -1947,8 +2083,8 @@
       <c r="S25" s="11"/>
       <c r="T25" s="8"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D26" s="12"/>
+    <row r="26" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -1959,11 +2095,7 @@
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D27" s="8"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+    <row r="27" spans="4:20" x14ac:dyDescent="0.2">
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
@@ -1971,11 +2103,7 @@
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+    <row r="28" spans="4:20" x14ac:dyDescent="0.2">
       <c r="H28" s="12"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
@@ -1984,8 +2112,8 @@
       <c r="M28" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:G11">
-    <sortCondition ref="C8:C11"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:G9">
+    <sortCondition ref="C8:C9"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1994,21 +2122,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF50480-301C-0843-A08D-1FF82088E86E}">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.5" bestFit="1" customWidth="1"/>
@@ -2029,16 +2151,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2054,24 +2176,24 @@
       <c r="S1" s="6"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="73">
+      <c r="B2" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70">
+        <v>0.39097744360902198</v>
+      </c>
+      <c r="E2" s="70">
+        <v>0.21804511278195399</v>
+      </c>
+      <c r="F2" s="73">
+        <v>0.30827067669172897</v>
+      </c>
+      <c r="G2" s="84">
         <v>8.2706766917293201E-2</v>
-      </c>
-      <c r="E2" s="73">
-        <v>0.30827067669172897</v>
-      </c>
-      <c r="F2" s="73">
-        <v>0.39097744360902198</v>
-      </c>
-      <c r="G2" s="75">
-        <v>0.21804511278195399</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -2088,24 +2210,24 @@
       <c r="T2" s="8"/>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="74">
+      <c r="B3" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="86"/>
+      <c r="D3" s="53">
+        <v>0</v>
+      </c>
+      <c r="E3" s="87">
+        <v>0.83739837398373895</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0</v>
+      </c>
+      <c r="G3" s="69">
         <v>0.16260162601625999</v>
-      </c>
-      <c r="E3" s="22">
-        <v>0</v>
-      </c>
-      <c r="F3" s="22">
-        <v>0</v>
-      </c>
-      <c r="G3" s="76">
-        <v>0.83739837398373895</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -2122,27 +2244,21 @@
       <c r="T3" s="8"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="87" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="77">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="33">
-        <v>0</v>
-      </c>
-      <c r="G4" s="34">
-        <v>0</v>
-      </c>
+      <c r="B4" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="72">
+        <v>1</v>
+      </c>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="55"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -2158,27 +2274,23 @@
       <c r="T4" s="8"/>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="79" t="s">
+      <c r="B5" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="78">
+      <c r="C5" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="60">
+        <v>0</v>
+      </c>
+      <c r="E5" s="75">
         <v>1</v>
       </c>
-      <c r="E5" s="22">
-        <v>0</v>
-      </c>
-      <c r="F5" s="48">
-        <v>0</v>
-      </c>
-      <c r="G5" s="50">
-        <v>0</v>
-      </c>
+      <c r="F5" s="59"/>
+      <c r="G5" s="91"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -2194,27 +2306,23 @@
       <c r="T5" s="8"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="79" t="s">
+      <c r="B6" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="88">
-        <v>3.3333333333333298E-2</v>
-      </c>
-      <c r="E6" s="58">
-        <v>0.96666666666666601</v>
-      </c>
-      <c r="F6" s="47">
-        <v>0</v>
-      </c>
-      <c r="G6" s="68">
-        <v>0</v>
-      </c>
+      <c r="C6" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="89"/>
+      <c r="E6" s="72">
+        <v>0.92307692307692302</v>
+      </c>
+      <c r="F6" s="92">
+        <v>7.69230769230769E-2</v>
+      </c>
+      <c r="G6" s="93"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -2230,27 +2338,21 @@
       <c r="T6" s="8"/>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="89">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="E7" s="81">
-        <v>0</v>
-      </c>
-      <c r="F7" s="22">
-        <v>0</v>
-      </c>
-      <c r="G7" s="82">
-        <v>0.66666666666666596</v>
-      </c>
+      <c r="B7" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="89"/>
+      <c r="E7" s="103">
+        <v>1</v>
+      </c>
+      <c r="F7" s="75"/>
+      <c r="G7" s="66"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="Q7" s="8"/>
@@ -2259,26 +2361,22 @@
       <c r="T7" s="8"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="79" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="85">
-        <v>0</v>
-      </c>
-      <c r="E8" s="90">
-        <v>7.69230769230769E-2</v>
-      </c>
-      <c r="F8" s="47">
-        <v>0</v>
-      </c>
-      <c r="G8" s="58">
-        <v>0.92307692307692302</v>
+      <c r="B8" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="100" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="94"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="72">
+        <v>0.96666666666666601</v>
+      </c>
+      <c r="G8" s="93">
+        <v>3.3333333333333298E-2</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -2288,26 +2386,24 @@
       <c r="T8" s="8"/>
     </row>
     <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="86">
+      <c r="B9" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="96"/>
+      <c r="E9" s="59">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="F9" s="60">
         <v>0</v>
       </c>
-      <c r="E9" s="48">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22">
-        <v>0</v>
-      </c>
-      <c r="G9" s="78">
-        <v>1</v>
+      <c r="G9" s="66">
+        <v>0.33333333333333298</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -2317,26 +2413,22 @@
       <c r="T9" s="8"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="83" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="85">
-        <v>0</v>
-      </c>
-      <c r="E10" s="47">
-        <v>0</v>
-      </c>
-      <c r="F10" s="58">
-        <v>1</v>
-      </c>
-      <c r="G10" s="39">
-        <v>0</v>
+      <c r="B10" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="94"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="72">
+        <v>0.5</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -2346,25 +2438,19 @@
       <c r="T10" s="8"/>
     </row>
     <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="84" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="66">
-        <v>0</v>
-      </c>
-      <c r="E11" s="37">
-        <v>0</v>
-      </c>
-      <c r="F11" s="59">
-        <v>0</v>
-      </c>
-      <c r="G11" s="91">
+      <c r="B11" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="85"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="103">
         <v>1</v>
       </c>
       <c r="H11" s="8"/>
@@ -2375,25 +2461,21 @@
       <c r="T11" s="8"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="92">
-        <v>0.15942028985507201</v>
-      </c>
-      <c r="E12" s="22">
-        <v>0.59420289855072395</v>
-      </c>
-      <c r="F12" s="71"/>
-      <c r="G12" s="39">
-        <v>0.24637681159420199</v>
-      </c>
+      <c r="B12" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="71">
+        <v>1</v>
+      </c>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="55"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="Q12" s="8"/>
@@ -2402,25 +2484,23 @@
       <c r="T12" s="8"/>
     </row>
     <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="42" t="s">
+      <c r="B13" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="78">
-        <v>0.36363636363636298</v>
-      </c>
-      <c r="E13" s="22">
+      <c r="C13" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="60">
         <v>0</v>
       </c>
-      <c r="F13" s="69"/>
-      <c r="G13" s="50">
-        <v>0.63636363636363602</v>
-      </c>
+      <c r="E13" s="75">
+        <v>1</v>
+      </c>
+      <c r="F13" s="59"/>
+      <c r="G13" s="91"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="Q13" s="8"/>
@@ -2429,25 +2509,21 @@
       <c r="T13" s="8"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="42" t="s">
+      <c r="B14" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="22">
-        <v>0.15942028985507201</v>
-      </c>
-      <c r="E14" s="58">
-        <v>0.59420289855072395</v>
-      </c>
-      <c r="F14" s="70"/>
-      <c r="G14" s="68">
-        <v>0.24637681159420199</v>
-      </c>
+      <c r="C14" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="89"/>
+      <c r="E14" s="72">
+        <v>1</v>
+      </c>
+      <c r="F14" s="92"/>
+      <c r="G14" s="93"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="Q14" s="10"/>
@@ -2456,25 +2532,21 @@
       <c r="T14" s="8"/>
     </row>
     <row r="15" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="48">
-        <v>0.36363636363636298</v>
-      </c>
-      <c r="E15" s="59">
-        <v>0</v>
-      </c>
-      <c r="F15" s="69"/>
-      <c r="G15" s="39">
-        <v>0.63636363636363602</v>
-      </c>
+      <c r="B15" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="96"/>
+      <c r="E15" s="103">
+        <v>1</v>
+      </c>
+      <c r="F15" s="59"/>
+      <c r="G15" s="66"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="Q15" s="11"/>
@@ -2483,45 +2555,150 @@
       <c r="T15" s="8"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="89"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75">
+        <v>0.6</v>
+      </c>
+      <c r="G16" s="72">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="85"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="22">
+      <c r="I19" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="12">
+        <v>0.63658026755852803</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.43323482510146499</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0.459334481428191</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0.38658026755852798</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2</v>
+      </c>
+      <c r="G20" s="12">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.20658529547014701</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.18525729405212099</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.103079113926654</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0.11918481905985399</v>
+      </c>
+      <c r="L20" s="8">
         <v>0</v>
       </c>
-      <c r="E16" s="22">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0.44642857142857101</v>
+      </c>
+      <c r="C21" s="8">
+        <v>7.3581660275208599E-2</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.12611714406330499</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.19642857142857101</v>
+      </c>
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.36552659804390503</v>
+      </c>
+      <c r="I21" s="8">
+        <v>6.0202593211829497E-2</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.103230862063993</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0.25314193980306898</v>
+      </c>
+      <c r="L21" s="8">
         <v>0</v>
-      </c>
-      <c r="F16" s="71"/>
-      <c r="G16" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="37">
-        <v>0</v>
-      </c>
-      <c r="E17" s="37">
-        <v>0</v>
-      </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="78">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2535,13 +2712,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99F23E7-3B71-1E4B-89E7-8EECD61E4DE0}">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.83203125" customWidth="1"/>
     <col min="15" max="15" width="7.33203125" customWidth="1"/>
@@ -2562,39 +2746,39 @@
     <col min="30" max="30" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="20" t="s">
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
@@ -2606,35 +2790,31 @@
       <c r="S1" s="6"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22">
-        <v>0</v>
-      </c>
-      <c r="E2" s="22">
+      <c r="B2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="113">
+        <v>8.4745762711864406E-3</v>
+      </c>
+      <c r="G2" s="113">
+        <v>5.9322033898305003E-2</v>
+      </c>
+      <c r="H2" s="40">
+        <v>2.5423728813559299E-2</v>
+      </c>
+      <c r="I2" s="113">
+        <v>0.144067796610169</v>
+      </c>
+      <c r="J2" s="113">
         <v>0.76271186440677896</v>
       </c>
-      <c r="F2" s="22">
-        <v>2.5423728813559299E-2</v>
-      </c>
-      <c r="G2" s="22">
-        <v>0.144067796610169</v>
-      </c>
-      <c r="H2" s="22">
-        <v>5.9322033898305003E-2</v>
-      </c>
-      <c r="I2" s="22">
-        <v>8.4745762711864406E-3</v>
-      </c>
-      <c r="J2" s="22">
-        <v>0</v>
-      </c>
-      <c r="K2" s="22">
+      <c r="K2" s="24">
         <v>0</v>
       </c>
       <c r="L2" s="8"/>
@@ -2647,37 +2827,33 @@
       <c r="S2" s="13"/>
       <c r="T2" s="8"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22">
+      <c r="B3" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="104">
+        <v>0</v>
+      </c>
+      <c r="G3" s="104">
+        <v>0</v>
+      </c>
+      <c r="H3" s="112">
+        <v>0.46376811594202899</v>
+      </c>
+      <c r="I3" s="104">
+        <v>0</v>
+      </c>
+      <c r="J3" s="104">
+        <v>0</v>
+      </c>
+      <c r="K3" s="41">
         <v>0.53623188405797095</v>
-      </c>
-      <c r="E3" s="22">
-        <v>0</v>
-      </c>
-      <c r="F3" s="22">
-        <v>0.46376811594202899</v>
-      </c>
-      <c r="G3" s="22">
-        <v>0</v>
-      </c>
-      <c r="H3" s="22">
-        <v>0</v>
-      </c>
-      <c r="I3" s="22">
-        <v>0</v>
-      </c>
-      <c r="J3" s="22">
-        <v>0</v>
-      </c>
-      <c r="K3" s="22">
-        <v>0</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -2690,39 +2866,29 @@
       <c r="T3" s="8"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="22">
-        <v>0</v>
-      </c>
-      <c r="E4" s="22">
-        <v>0.88636363636363602</v>
-      </c>
-      <c r="F4" s="22">
-        <v>4.54545454545454E-2</v>
-      </c>
-      <c r="G4" s="22">
-        <v>2.27272727272727E-2</v>
-      </c>
-      <c r="H4" s="22">
-        <v>4.54545454545454E-2</v>
-      </c>
-      <c r="I4" s="22">
-        <v>0</v>
-      </c>
-      <c r="J4" s="22">
-        <v>0</v>
-      </c>
-      <c r="K4" s="22">
-        <v>0</v>
-      </c>
+      <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="78"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="72">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H4" s="23">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I4" s="23">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="24"/>
       <c r="L4" s="8"/>
       <c r="M4" s="12"/>
       <c r="N4" s="8"/>
@@ -2733,39 +2899,29 @@
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="22">
+      <c r="B5" s="104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="108"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="34">
         <v>0</v>
       </c>
-      <c r="E5" s="22">
-        <v>1</v>
-      </c>
-      <c r="F5" s="22">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0</v>
-      </c>
-      <c r="H5" s="22">
-        <v>0</v>
-      </c>
-      <c r="I5" s="22">
-        <v>0</v>
-      </c>
-      <c r="J5" s="22">
-        <v>0</v>
-      </c>
-      <c r="K5" s="22">
-        <v>0</v>
+      <c r="H5" s="104">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="32">
+        <v>0.5</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
@@ -2778,39 +2934,33 @@
       <c r="T5" s="8"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22">
-        <v>0</v>
-      </c>
-      <c r="E6" s="22">
+      <c r="B6" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="30">
+        <v>1.53846153846153E-2</v>
+      </c>
+      <c r="G6" s="104">
+        <v>7.69230769230769E-2</v>
+      </c>
+      <c r="H6" s="114">
+        <v>1.53846153846153E-2</v>
+      </c>
+      <c r="I6" s="30">
+        <v>0.246153846153846</v>
+      </c>
+      <c r="J6" s="30">
         <v>0.64615384615384597</v>
       </c>
-      <c r="F6" s="22">
-        <v>1.53846153846153E-2</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.246153846153846</v>
-      </c>
-      <c r="H6" s="22">
-        <v>7.69230769230769E-2</v>
-      </c>
-      <c r="I6" s="22">
-        <v>1.53846153846153E-2</v>
-      </c>
-      <c r="J6" s="22">
-        <v>0</v>
-      </c>
-      <c r="K6" s="22">
-        <v>0</v>
-      </c>
+      <c r="K6" s="39"/>
       <c r="L6" s="8"/>
       <c r="M6" s="12"/>
       <c r="N6" s="8"/>
@@ -2821,737 +2971,554 @@
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="108"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="103">
+        <v>1</v>
+      </c>
+      <c r="I7" s="104"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="109"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="30">
+        <v>4.54545454545454E-2</v>
+      </c>
+      <c r="G8" s="30">
+        <v>0.18181818181818099</v>
+      </c>
+      <c r="H8" s="104"/>
+      <c r="I8" s="72">
+        <v>0.59090909090909005</v>
+      </c>
+      <c r="J8" s="30">
+        <v>0.18181818181818099</v>
+      </c>
+      <c r="K8" s="39"/>
+    </row>
+    <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="108"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31">
+        <v>1</v>
+      </c>
+      <c r="I9" s="34">
+        <v>0</v>
+      </c>
+      <c r="J9" s="104"/>
+      <c r="K9" s="32"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="109"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="72">
+        <v>1</v>
+      </c>
+      <c r="K10" s="39"/>
+    </row>
+    <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="108"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="34">
+        <v>0</v>
+      </c>
+      <c r="K11" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="111"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104">
+        <v>4.54545454545454E-2</v>
+      </c>
+      <c r="H12" s="104">
+        <v>4.54545454545454E-2</v>
+      </c>
+      <c r="I12" s="104">
+        <v>2.27272727272727E-2</v>
+      </c>
+      <c r="J12" s="104">
+        <v>0.88636363636363602</v>
+      </c>
+      <c r="K12" s="33"/>
+    </row>
+    <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="80"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="78"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="23">
+        <v>1</v>
+      </c>
+      <c r="H14" s="33">
+        <v>0</v>
+      </c>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+    </row>
+    <row r="15" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="108"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="103">
+        <v>1</v>
+      </c>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="29"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="111"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104">
+        <v>1</v>
+      </c>
+      <c r="K16" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="80"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="I20" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="82" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0.31201551973249397</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.50613093966913103</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.372798116322552</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.14534885306582701</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0.19793055234314999</v>
+      </c>
+      <c r="I21" s="7">
+        <v>0.33505019870431901</v>
+      </c>
+      <c r="J21" s="7">
+        <v>0.23730272762931201</v>
+      </c>
+      <c r="K21" s="7">
+        <v>0.110430996554312</v>
+      </c>
+      <c r="L21" s="7">
+        <v>0.48989794855663499</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="12">
+        <v>0.13888888888888801</v>
+      </c>
+      <c r="C22" s="7">
+        <v>4.7398144413069703E-3</v>
+      </c>
+      <c r="D22" s="12">
+        <v>9.1599222034004606E-3</v>
+      </c>
+      <c r="E22" s="12">
+        <v>-2.77777777777777E-2</v>
+      </c>
+      <c r="F22" s="7">
+        <v>2</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0.202225274702236</v>
+      </c>
+      <c r="I22" s="7">
+        <v>6.7154891240413898E-3</v>
+      </c>
+      <c r="J22" s="7">
+        <v>1.29832238356211E-2</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0.17458386335053899</v>
+      </c>
+      <c r="L22" s="7">
         <v>0</v>
       </c>
-      <c r="E7" s="22">
-        <v>0.18181818181818099</v>
-      </c>
-      <c r="F7" s="22">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.59090909090909005</v>
-      </c>
-      <c r="H7" s="22">
-        <v>0.18181818181818099</v>
-      </c>
-      <c r="I7" s="22">
-        <v>4.54545454545454E-2</v>
-      </c>
-      <c r="J7" s="22">
-        <v>0</v>
-      </c>
-      <c r="K7" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="22">
-        <v>0</v>
-      </c>
-      <c r="E8" s="22">
-        <v>0</v>
-      </c>
-      <c r="F8" s="22">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="G8" s="22">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="H8" s="22">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0</v>
-      </c>
-      <c r="J8" s="22">
-        <v>0</v>
-      </c>
-      <c r="K8" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="22">
-        <v>1</v>
-      </c>
-      <c r="E9" s="22">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22">
-        <v>0</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0</v>
-      </c>
-      <c r="I9" s="22">
-        <v>0</v>
-      </c>
-      <c r="J9" s="22">
-        <v>0</v>
-      </c>
-      <c r="K9" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="22">
-        <v>1</v>
-      </c>
-      <c r="E10" s="22">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0</v>
-      </c>
-      <c r="I10" s="22">
-        <v>0</v>
-      </c>
-      <c r="J10" s="22">
-        <v>0</v>
-      </c>
-      <c r="K10" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="22">
-        <v>0</v>
-      </c>
-      <c r="E11" s="22">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1</v>
-      </c>
-      <c r="G11" s="22">
-        <v>0</v>
-      </c>
-      <c r="H11" s="22">
-        <v>0</v>
-      </c>
-      <c r="I11" s="22">
-        <v>0</v>
-      </c>
-      <c r="J11" s="22">
-        <v>0</v>
-      </c>
-      <c r="K11" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="22">
-        <v>0</v>
-      </c>
-      <c r="E12" s="22">
-        <v>0</v>
-      </c>
-      <c r="F12" s="22">
-        <v>1</v>
-      </c>
-      <c r="G12" s="22">
-        <v>0</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0</v>
-      </c>
-      <c r="I12" s="22">
-        <v>0</v>
-      </c>
-      <c r="J12" s="22">
-        <v>0</v>
-      </c>
-      <c r="K12" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="22">
-        <v>0</v>
-      </c>
-      <c r="F13" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="22">
-        <v>0</v>
-      </c>
-      <c r="H13" s="22">
-        <v>0</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0</v>
-      </c>
-      <c r="J13" s="22">
-        <v>0</v>
-      </c>
-      <c r="K13" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="22">
-        <v>0</v>
-      </c>
-      <c r="E14" s="22">
-        <v>0.90566037735849003</v>
-      </c>
-      <c r="F14" s="22">
-        <v>3.7735849056603703E-2</v>
-      </c>
-      <c r="G14" s="22">
-        <v>1.8867924528301799E-2</v>
-      </c>
-      <c r="H14" s="22">
-        <v>3.7735849056603703E-2</v>
-      </c>
-      <c r="I14" s="22">
-        <v>0</v>
-      </c>
-      <c r="J14" s="22">
-        <v>0</v>
-      </c>
-      <c r="K14" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="22">
-        <v>0</v>
-      </c>
-      <c r="E15" s="22">
-        <v>0.90566037735849003</v>
-      </c>
-      <c r="F15" s="22">
-        <v>3.7735849056603703E-2</v>
-      </c>
-      <c r="G15" s="22">
-        <v>1.8867924528301799E-2</v>
-      </c>
-      <c r="H15" s="22">
-        <v>3.7735849056603703E-2</v>
-      </c>
-      <c r="I15" s="22">
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
-        <v>0</v>
-      </c>
-      <c r="K15" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="22">
-        <v>0</v>
-      </c>
-      <c r="E16" s="22">
-        <v>0</v>
-      </c>
-      <c r="F16" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="22">
-        <v>0</v>
-      </c>
-      <c r="H16" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="22">
-        <v>0</v>
-      </c>
-      <c r="J16" s="22">
-        <v>0</v>
-      </c>
-      <c r="K16" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="22">
-        <v>1</v>
-      </c>
-      <c r="E17" s="22">
-        <v>0</v>
-      </c>
-      <c r="F17" s="22">
-        <v>0</v>
-      </c>
-      <c r="G17" s="22">
-        <v>0</v>
-      </c>
-      <c r="H17" s="22">
-        <v>0</v>
-      </c>
-      <c r="I17" s="22">
-        <v>0</v>
-      </c>
-      <c r="J17" s="22">
-        <v>0</v>
-      </c>
-      <c r="K17" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="22">
-        <v>1</v>
-      </c>
-      <c r="E18" s="22">
-        <v>0</v>
-      </c>
-      <c r="F18" s="22">
-        <v>0</v>
-      </c>
-      <c r="G18" s="22">
-        <v>0</v>
-      </c>
-      <c r="H18" s="22">
-        <v>0</v>
-      </c>
-      <c r="I18" s="22">
-        <v>0</v>
-      </c>
-      <c r="J18" s="22">
-        <v>0</v>
-      </c>
-      <c r="K18" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="22">
-        <v>0</v>
-      </c>
-      <c r="F19" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="G19" s="22">
-        <v>0</v>
-      </c>
-      <c r="H19" s="22">
-        <v>0</v>
-      </c>
-      <c r="I19" s="22">
-        <v>0</v>
-      </c>
-      <c r="J19" s="22">
-        <v>0</v>
-      </c>
-      <c r="K19" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D24" s="8"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D25" s="8"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D26" s="8"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.2">
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.2">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+    </row>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.2">
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+    </row>
+    <row r="36" spans="4:11" x14ac:dyDescent="0.2">
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+    </row>
+    <row r="37" spans="4:11" x14ac:dyDescent="0.2">
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+    </row>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.2">
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A23:K40">
-    <sortCondition ref="C23:C40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A21:K38">
+    <sortCondition ref="C21:C38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
